--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_384_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_384_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>41:24</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>39.5%</t>
         </is>
       </c>
     </row>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>04:28</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -1727,16 +1727,16 @@
         <v>15</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>6</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>55:38</t>
+          <t>25:39</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>24:44</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2039,17 +2039,17 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>52:03</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>7.0%</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>24:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,22 +2431,22 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>9.5%</t>
         </is>
       </c>
     </row>
@@ -2514,13 +2514,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>7</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>52:19</t>
+          <t>22:20</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>20.6%</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>38:35</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>32.6%</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>27:40</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3019,17 +3019,17 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>25:10</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AN26" t="n">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
@@ -3491,16 +3491,16 @@
         <v>11</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>4</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>43:34</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AN28" t="n">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
     </row>
@@ -3827,16 +3827,16 @@
         <v>118</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>32</v>
@@ -4292,10 +4292,10 @@
         <v>5</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>57:12</t>
+          <t>27:12</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>20.9%</t>
         </is>
       </c>
     </row>
@@ -4488,10 +4488,10 @@
         <v>6</v>
       </c>
       <c r="T36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>35:36</t>
+          <t>25:37</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,17 +4604,17 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
@@ -4684,10 +4684,10 @@
         <v>4</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>36:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,17 +4800,17 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
@@ -4880,16 +4880,16 @@
         <v>22</v>
       </c>
       <c r="T38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>5</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>47:10</t>
+          <t>27:11</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>31:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5192,17 +5192,17 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
@@ -5272,10 +5272,10 @@
         <v>10</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>25:05</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,17 +5388,17 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>33:03</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AN41" t="n">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>63:52</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5976,22 +5976,22 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>24.8%</t>
         </is>
       </c>
     </row>
@@ -6062,10 +6062,10 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
         <v>9</v>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>62:07</t>
+          <t>32:08</t>
         </is>
       </c>
       <c r="AN44" t="n">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>41.9%</t>
         </is>
       </c>
     </row>
@@ -6392,16 +6392,16 @@
         <v>79</v>
       </c>
       <c r="T46" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>23</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_384_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_384_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
@@ -1727,16 +1727,16 @@
         <v>15</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>6</v>
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
@@ -2514,13 +2514,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X23" t="n">
         <v>7</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3491,16 +3491,16 @@
         <v>11</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
         <v>4</v>
@@ -3827,16 +3827,16 @@
         <v>118</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X30" t="n">
         <v>32</v>
@@ -4292,10 +4292,10 @@
         <v>5</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4488,10 +4488,10 @@
         <v>6</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4684,10 +4684,10 @@
         <v>4</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4880,16 +4880,16 @@
         <v>22</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
         <v>5</v>
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5272,10 +5272,10 @@
         <v>10</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -6062,10 +6062,10 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X44" t="n">
         <v>9</v>
@@ -6392,16 +6392,16 @@
         <v>79</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X46" t="n">
         <v>23</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_384_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_384_EL.xlsx
@@ -674,10 +674,10 @@
         <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="O2" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -692,20 +692,20 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>84.00</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>31.82</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="P3" t="n">
         <v>10</v>
@@ -854,17 +854,17 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V3" t="n">
         <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>67.65</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1739,10 +1739,10 @@
         <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
@@ -1783,14 +1783,14 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -2327,14 +2327,14 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2523,14 +2523,14 @@
         <v>2</v>
       </c>
       <c r="X23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2719,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3111,10 +3111,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -3503,10 +3503,10 @@
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>6</v>
       </c>
       <c r="X30" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Y30" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4500,10 +4500,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
@@ -4892,14 +4892,14 @@
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -6068,10 +6068,10 @@
         <v>4</v>
       </c>
       <c r="X44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -6404,14 +6404,14 @@
         <v>5</v>
       </c>
       <c r="X46" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="Y46" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6440,22 +6440,22 @@
         <v>2</v>
       </c>
       <c r="AH46" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="AJ46" t="n">
         <v>2</v>
       </c>
       <c r="AK46" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
